--- a/Laporan Keuangan Karim Gadget ID.xlsx
+++ b/Laporan Keuangan Karim Gadget ID.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Coding\Laporan Keuangan - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{097890D7-F001-4F32-A652-2C8CD26C364C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC66CB34-D11A-4BF1-B293-DB2C9B8730AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ag-Sep" sheetId="1" r:id="rId1"/>
